--- a/artfynd/A 18238-2024 artfynd.xlsx
+++ b/artfynd/A 18238-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117676094</v>
       </c>
       <c r="B2" t="n">
-        <v>91270</v>
+        <v>91272</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117783195</v>
+        <v>117827288</v>
       </c>
       <c r="B3" t="n">
-        <v>90513</v>
+        <v>78482</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,13 +824,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475553</v>
+        <v>475579</v>
       </c>
       <c r="R3" t="n">
-        <v>7026419</v>
+        <v>7026483</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -854,12 +854,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-07</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-07</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,14 +887,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>Låga</t>
-        </is>
-      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies # Låga</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -912,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117827288</v>
+        <v>117783195</v>
       </c>
       <c r="B4" t="n">
-        <v>78480</v>
+        <v>90515</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -955,13 +950,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475579</v>
+        <v>475553</v>
       </c>
       <c r="R4" t="n">
-        <v>7026483</v>
+        <v>7026419</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -985,12 +980,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,9 +1013,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Låga</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Låga</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
